--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariano\Desktop\stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12737187-D518-464C-9EC2-9D1E846B63DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC346D0-8AE0-4EA9-BDC0-6F779B433A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EE8A0F23-18C3-4A4D-8D5C-85AD26929363}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="529">
   <si>
     <t>Producto</t>
   </si>
@@ -564,9 +564,6 @@
     <t>LUCA MALBEC 23 6X750  B/LAURA</t>
   </si>
   <si>
-    <t>356.00</t>
-  </si>
-  <si>
     <t>1677-24</t>
   </si>
   <si>
@@ -705,9 +702,6 @@
     <t>DV CATENA MB-MB 24 6X750 MI</t>
   </si>
   <si>
-    <t>972.00</t>
-  </si>
-  <si>
     <t>2201-21</t>
   </si>
   <si>
@@ -1020,9 +1014,6 @@
     <t>SAINT FELICIEN MB 25 12X375</t>
   </si>
   <si>
-    <t>43.00</t>
-  </si>
-  <si>
     <t>2654-24</t>
   </si>
   <si>
@@ -1134,9 +1125,6 @@
     <t>CAT ZAP MB ARG.23 6X750 ENV HZ</t>
   </si>
   <si>
-    <t>150.00</t>
-  </si>
-  <si>
     <t>295-21</t>
   </si>
   <si>
@@ -1149,9 +1137,6 @@
     <t>ANGELICA ZAP. MALBEC 22 4X750</t>
   </si>
   <si>
-    <t>42.00</t>
-  </si>
-  <si>
     <t>296-18</t>
   </si>
   <si>
@@ -1329,9 +1314,6 @@
     <t>NICASIA VINEY BL BL 25 6X75 SC</t>
   </si>
   <si>
-    <t>424.00</t>
-  </si>
-  <si>
     <t>435-24</t>
   </si>
   <si>
@@ -1347,12 +1329,6 @@
     <t>736.00</t>
   </si>
   <si>
-    <t>4803-18</t>
-  </si>
-  <si>
-    <t>ENEMIGO AS BRAVAS MB 18 6X75</t>
-  </si>
-  <si>
     <t>4820-23</t>
   </si>
   <si>
@@ -1627,6 +1603,24 @@
   </si>
   <si>
     <t>CUADRO ALAMOS MADERA</t>
+  </si>
+  <si>
+    <t>355.00</t>
+  </si>
+  <si>
+    <t>969.00</t>
+  </si>
+  <si>
+    <t>58.00</t>
+  </si>
+  <si>
+    <t>38.00</t>
+  </si>
+  <si>
+    <t>148.00</t>
+  </si>
+  <si>
+    <t>421.00</t>
   </si>
 </sst>
 </file>
@@ -1978,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC5E5D4-D349-4ED3-89BE-BCC9AFEC568D}">
-  <dimension ref="A1:C221"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -2664,7 +2658,7 @@
         <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,37 +2801,37 @@
         <v>175</v>
       </c>
       <c r="C75" t="s">
-        <v>176</v>
+        <v>523</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
         <v>177</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>178</v>
-      </c>
-      <c r="C76" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>179</v>
+      </c>
+      <c r="B77" t="s">
         <v>180</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>181</v>
-      </c>
-      <c r="C77" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
         <v>183</v>
-      </c>
-      <c r="B78" t="s">
-        <v>184</v>
       </c>
       <c r="C78" t="s">
         <v>150</v>
@@ -2845,10 +2839,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" t="s">
         <v>185</v>
-      </c>
-      <c r="B79" t="s">
-        <v>186</v>
       </c>
       <c r="C79" t="s">
         <v>8</v>
@@ -2856,21 +2850,21 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>186</v>
+      </c>
+      <c r="B80" t="s">
         <v>187</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>188</v>
-      </c>
-      <c r="C80" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" t="s">
         <v>190</v>
-      </c>
-      <c r="B81" t="s">
-        <v>191</v>
       </c>
       <c r="C81" t="s">
         <v>133</v>
@@ -2878,21 +2872,21 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B82" t="s">
         <v>192</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>193</v>
-      </c>
-      <c r="C82" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>194</v>
+      </c>
+      <c r="B83" t="s">
         <v>195</v>
-      </c>
-      <c r="B83" t="s">
-        <v>196</v>
       </c>
       <c r="C83" t="s">
         <v>167</v>
@@ -2900,32 +2894,32 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>196</v>
+      </c>
+      <c r="B84" t="s">
         <v>197</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>198</v>
-      </c>
-      <c r="C84" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>199</v>
+      </c>
+      <c r="B85" t="s">
         <v>200</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>201</v>
-      </c>
-      <c r="C85" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>202</v>
+      </c>
+      <c r="B86" t="s">
         <v>203</v>
-      </c>
-      <c r="B86" t="s">
-        <v>204</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -2933,10 +2927,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" t="s">
         <v>205</v>
-      </c>
-      <c r="B87" t="s">
-        <v>206</v>
       </c>
       <c r="C87" t="s">
         <v>133</v>
@@ -2944,32 +2938,32 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>206</v>
+      </c>
+      <c r="B88" t="s">
         <v>207</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>208</v>
-      </c>
-      <c r="C88" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>209</v>
+      </c>
+      <c r="B89" t="s">
         <v>210</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>211</v>
-      </c>
-      <c r="C89" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>212</v>
+      </c>
+      <c r="B90" t="s">
         <v>213</v>
-      </c>
-      <c r="B90" t="s">
-        <v>214</v>
       </c>
       <c r="C90" t="s">
         <v>26</v>
@@ -2977,54 +2971,54 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>214</v>
+      </c>
+      <c r="B91" t="s">
         <v>215</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>216</v>
-      </c>
-      <c r="C91" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>217</v>
+      </c>
+      <c r="B92" t="s">
         <v>218</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>219</v>
-      </c>
-      <c r="C92" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>220</v>
+      </c>
+      <c r="B93" t="s">
         <v>221</v>
       </c>
-      <c r="B93" t="s">
-        <v>222</v>
-      </c>
       <c r="C93" t="s">
-        <v>223</v>
+        <v>524</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>222</v>
+      </c>
+      <c r="B94" t="s">
+        <v>223</v>
+      </c>
+      <c r="C94" t="s">
         <v>224</v>
-      </c>
-      <c r="B94" t="s">
-        <v>225</v>
-      </c>
-      <c r="C94" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
         <v>41</v>
@@ -3032,21 +3026,21 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>227</v>
+      </c>
+      <c r="B96" t="s">
+        <v>228</v>
+      </c>
+      <c r="C96" t="s">
         <v>229</v>
-      </c>
-      <c r="B96" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C97" t="s">
         <v>30</v>
@@ -3054,21 +3048,21 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>232</v>
+      </c>
+      <c r="B98" t="s">
+        <v>233</v>
+      </c>
+      <c r="C98" t="s">
         <v>234</v>
-      </c>
-      <c r="B98" t="s">
-        <v>235</v>
-      </c>
-      <c r="C98" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C99" t="s">
         <v>22</v>
@@ -3076,10 +3070,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B100" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C100" t="s">
         <v>41</v>
@@ -3087,10 +3081,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
         <v>124</v>
@@ -3098,21 +3092,21 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>241</v>
+      </c>
+      <c r="B102" t="s">
+        <v>242</v>
+      </c>
+      <c r="C102" t="s">
         <v>243</v>
-      </c>
-      <c r="B102" t="s">
-        <v>244</v>
-      </c>
-      <c r="C102" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C103" t="s">
         <v>26</v>
@@ -3120,21 +3114,21 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>246</v>
+      </c>
+      <c r="B104" t="s">
+        <v>247</v>
+      </c>
+      <c r="C104" t="s">
         <v>248</v>
-      </c>
-      <c r="B104" t="s">
-        <v>249</v>
-      </c>
-      <c r="C104" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B105" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C105" t="s">
         <v>8</v>
@@ -3142,10 +3136,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C106" t="s">
         <v>26</v>
@@ -3153,10 +3147,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C107" t="s">
         <v>16</v>
@@ -3164,10 +3158,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -3175,10 +3169,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C109" t="s">
         <v>16</v>
@@ -3186,98 +3180,98 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>259</v>
+      </c>
+      <c r="B110" t="s">
+        <v>260</v>
+      </c>
+      <c r="C110" t="s">
         <v>261</v>
-      </c>
-      <c r="B110" t="s">
-        <v>262</v>
-      </c>
-      <c r="C110" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B111" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C111" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>264</v>
+      </c>
+      <c r="B112" t="s">
+        <v>265</v>
+      </c>
+      <c r="C112" t="s">
         <v>266</v>
-      </c>
-      <c r="B112" t="s">
-        <v>267</v>
-      </c>
-      <c r="C112" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>267</v>
+      </c>
+      <c r="B113" t="s">
+        <v>268</v>
+      </c>
+      <c r="C113" t="s">
         <v>269</v>
-      </c>
-      <c r="B113" t="s">
-        <v>270</v>
-      </c>
-      <c r="C113" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>270</v>
+      </c>
+      <c r="B114" t="s">
+        <v>271</v>
+      </c>
+      <c r="C114" t="s">
         <v>272</v>
-      </c>
-      <c r="B114" t="s">
-        <v>273</v>
-      </c>
-      <c r="C114" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B115" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C115" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>275</v>
+      </c>
+      <c r="B116" t="s">
+        <v>276</v>
+      </c>
+      <c r="C116" t="s">
         <v>277</v>
-      </c>
-      <c r="B116" t="s">
-        <v>278</v>
-      </c>
-      <c r="C116" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B117" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C117" t="s">
-        <v>282</v>
+        <v>525</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B118" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C118" t="s">
         <v>49</v>
@@ -3285,98 +3279,98 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>283</v>
+      </c>
+      <c r="B119" t="s">
+        <v>284</v>
+      </c>
+      <c r="C119" t="s">
         <v>285</v>
-      </c>
-      <c r="B119" t="s">
-        <v>286</v>
-      </c>
-      <c r="C119" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>286</v>
+      </c>
+      <c r="B120" t="s">
+        <v>287</v>
+      </c>
+      <c r="C120" t="s">
         <v>288</v>
-      </c>
-      <c r="B120" t="s">
-        <v>289</v>
-      </c>
-      <c r="C120" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C121" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>291</v>
+      </c>
+      <c r="B122" t="s">
+        <v>292</v>
+      </c>
+      <c r="C122" t="s">
         <v>293</v>
-      </c>
-      <c r="B122" t="s">
-        <v>294</v>
-      </c>
-      <c r="C122" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>294</v>
+      </c>
+      <c r="B123" t="s">
+        <v>295</v>
+      </c>
+      <c r="C123" t="s">
         <v>296</v>
-      </c>
-      <c r="B123" t="s">
-        <v>297</v>
-      </c>
-      <c r="C123" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>297</v>
+      </c>
+      <c r="B124" t="s">
+        <v>298</v>
+      </c>
+      <c r="C124" t="s">
         <v>299</v>
-      </c>
-      <c r="B124" t="s">
-        <v>300</v>
-      </c>
-      <c r="C124" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>300</v>
+      </c>
+      <c r="B125" t="s">
+        <v>301</v>
+      </c>
+      <c r="C125" t="s">
         <v>302</v>
-      </c>
-      <c r="B125" t="s">
-        <v>303</v>
-      </c>
-      <c r="C125" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B126" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C126" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B127" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C127" t="s">
         <v>86</v>
@@ -3384,87 +3378,87 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>307</v>
+      </c>
+      <c r="B128" t="s">
+        <v>308</v>
+      </c>
+      <c r="C128" t="s">
         <v>309</v>
-      </c>
-      <c r="B128" t="s">
-        <v>310</v>
-      </c>
-      <c r="C128" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>310</v>
+      </c>
+      <c r="B129" t="s">
+        <v>311</v>
+      </c>
+      <c r="C129" t="s">
         <v>312</v>
-      </c>
-      <c r="B129" t="s">
-        <v>313</v>
-      </c>
-      <c r="C129" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>313</v>
+      </c>
+      <c r="B130" t="s">
+        <v>314</v>
+      </c>
+      <c r="C130" t="s">
         <v>315</v>
-      </c>
-      <c r="B130" t="s">
-        <v>316</v>
-      </c>
-      <c r="C130" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B131" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C131" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B132" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C132" t="s">
-        <v>322</v>
+        <v>139</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>321</v>
+      </c>
+      <c r="B133" t="s">
+        <v>322</v>
+      </c>
+      <c r="C133" t="s">
         <v>323</v>
-      </c>
-      <c r="B133" t="s">
-        <v>324</v>
-      </c>
-      <c r="C133" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B134" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C134" t="s">
-        <v>328</v>
+        <v>526</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B135" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C135" t="s">
         <v>124</v>
@@ -3472,43 +3466,43 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C136" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B137" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C137" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B138" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C138" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B139" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C139" t="s">
         <v>62</v>
@@ -3516,10 +3510,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B140" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C140" t="s">
         <v>124</v>
@@ -3527,10 +3521,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B141" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C141" t="s">
         <v>97</v>
@@ -3538,54 +3532,54 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B142" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C142" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B143" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C143" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B144" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C144" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B145" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C145" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B146" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C146" t="s">
         <v>30</v>
@@ -3593,10 +3587,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B147" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C147" t="s">
         <v>124</v>
@@ -3604,10 +3598,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B148" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C148" t="s">
         <v>86</v>
@@ -3615,10 +3609,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B149" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C149" t="s">
         <v>86</v>
@@ -3626,43 +3620,43 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B150" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C150" t="s">
-        <v>366</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B151" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C151" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B152" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C152" t="s">
-        <v>371</v>
+        <v>121</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B153" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -3670,21 +3664,21 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B154" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C154" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B155" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C155" t="s">
         <v>16</v>
@@ -3692,43 +3686,43 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B156" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C156" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B157" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C157" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B158" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C158" t="s">
-        <v>279</v>
+        <v>144</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B159" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="C159" t="s">
         <v>97</v>
@@ -3736,32 +3730,32 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B160" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C160" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B161" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C161" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B162" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="C162" t="s">
         <v>30</v>
@@ -3769,10 +3763,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B163" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C163" t="s">
         <v>26</v>
@@ -3780,54 +3774,54 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B164" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C164" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C165" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B166" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C166" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C167" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C168" t="s">
         <v>16</v>
@@ -3835,10 +3829,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B169" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C169" t="s">
         <v>12</v>
@@ -3846,21 +3840,21 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B170" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C170" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="B171" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C171" t="s">
         <v>26</v>
@@ -3868,32 +3862,32 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B172" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C172" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B173" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C173" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="B174" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C174" t="s">
         <v>133</v>
@@ -3901,494 +3895,494 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B175" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C175" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B176" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C176" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B177" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C177" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B178" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C178" t="s">
-        <v>431</v>
+        <v>528</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="B179" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C179" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B180" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C180" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B181" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C181" t="s">
-        <v>209</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B182" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C182" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B183" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C183" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B184" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C184" t="s">
-        <v>44</v>
+        <v>439</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B185" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C185" t="s">
-        <v>447</v>
+        <v>234</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B186" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C186" t="s">
-        <v>236</v>
+        <v>444</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B187" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C187" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B188" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C188" t="s">
-        <v>455</v>
+        <v>415</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B189" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C189" t="s">
-        <v>420</v>
+        <v>108</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B190" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="C190" t="s">
-        <v>108</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B191" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C191" t="s">
-        <v>462</v>
+        <v>53</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="B192" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="C192" t="s">
-        <v>53</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B193" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C193" t="s">
-        <v>467</v>
+        <v>75</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B194" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="C194" t="s">
-        <v>75</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B195" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C195" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B196" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C196" t="s">
-        <v>475</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B197" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C197" t="s">
-        <v>30</v>
+        <v>346</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B198" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C198" t="s">
-        <v>349</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B199" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="C199" t="s">
-        <v>202</v>
+        <v>476</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B200" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C200" t="s">
-        <v>484</v>
+        <v>41</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B201" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C201" t="s">
-        <v>41</v>
+        <v>481</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B202" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C202" t="s">
-        <v>489</v>
+        <v>14</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B203" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="C203" t="s">
-        <v>14</v>
+        <v>315</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B204" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C204" t="s">
-        <v>317</v>
+        <v>14</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B205" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="C205" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B206" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C206" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B207" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="C207" t="s">
-        <v>236</v>
+        <v>133</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B208" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="C208" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B209" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="C209" t="s">
-        <v>217</v>
+        <v>498</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B210" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C210" t="s">
-        <v>506</v>
+        <v>296</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="B211" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C211" t="s">
-        <v>298</v>
+        <v>86</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="B212" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C212" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B213" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="C213" t="s">
-        <v>24</v>
+        <v>507</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B214" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C214" t="s">
-        <v>515</v>
+        <v>280</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B215" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C215" t="s">
-        <v>282</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B216" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C216" t="s">
-        <v>520</v>
+        <v>323</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="B217" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C217" t="s">
-        <v>325</v>
+        <v>133</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B218" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="C218" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="B219" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C219" t="s">
         <v>16</v>
@@ -4396,23 +4390,12 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="B220" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C220" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>529</v>
-      </c>
-      <c r="B221" t="s">
-        <v>530</v>
-      </c>
-      <c r="C221" t="s">
         <v>26</v>
       </c>
     </row>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariano\Desktop\stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB961048-3403-4586-B6DE-A0A6420877C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABC30C2-D125-4965-82D8-4882CB8E012B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EE8A0F23-18C3-4A4D-8D5C-85AD26929363}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="516">
   <si>
     <t>Producto</t>
   </si>
@@ -333,9 +333,6 @@
     <t>TIKAL AMORIO 22 6X750 B/IMP</t>
   </si>
   <si>
-    <t>105.00</t>
-  </si>
-  <si>
     <t>1441-21</t>
   </si>
   <si>
@@ -414,15 +411,6 @@
     <t>96.00</t>
   </si>
   <si>
-    <t>1590-21</t>
-  </si>
-  <si>
-    <t>DVC TRIBUTO ANT ARG MB 21 4X75</t>
-  </si>
-  <si>
-    <t>32.00</t>
-  </si>
-  <si>
     <t>1600-18</t>
   </si>
   <si>
@@ -555,12 +543,6 @@
     <t>47.00</t>
   </si>
   <si>
-    <t>1941-NV</t>
-  </si>
-  <si>
-    <t>VERMOUTH VINCENZO 4X950CC</t>
-  </si>
-  <si>
     <t>2019-24</t>
   </si>
   <si>
@@ -813,12 +795,6 @@
     <t>168.00</t>
   </si>
   <si>
-    <t>2372-24</t>
-  </si>
-  <si>
-    <t>DV CATENA CS-MB 24 6X750 B/EL</t>
-  </si>
-  <si>
     <t>2372-24-EST</t>
   </si>
   <si>
@@ -891,12 +867,6 @@
     <t>SAINT FELICIE C.FRANC 24 6X750</t>
   </si>
   <si>
-    <t>2545-25</t>
-  </si>
-  <si>
-    <t>SF MALBEC 25 6X750 B/ELIT</t>
-  </si>
-  <si>
     <t>2546-25</t>
   </si>
   <si>
@@ -1188,12 +1158,6 @@
     <t>NICASIA BLEND HISTORIC 25 6X75</t>
   </si>
   <si>
-    <t>421-25MI</t>
-  </si>
-  <si>
-    <t>NICASIA VINE CS-FR 25 6X750</t>
-  </si>
-  <si>
     <t>422-24</t>
   </si>
   <si>
@@ -1287,12 +1251,6 @@
     <t>54.00</t>
   </si>
   <si>
-    <t>493-23</t>
-  </si>
-  <si>
-    <t>EL ENEMIGO CF 23 6X75 MI</t>
-  </si>
-  <si>
     <t>496-19</t>
   </si>
   <si>
@@ -1482,18 +1440,12 @@
     <t>CUADRO ALAMOS MADERA</t>
   </si>
   <si>
-    <t>38.00</t>
-  </si>
-  <si>
     <t>78.00</t>
   </si>
   <si>
     <t>10.00</t>
   </si>
   <si>
-    <t>15.00</t>
-  </si>
-  <si>
     <t>2212-23</t>
   </si>
   <si>
@@ -1503,9 +1455,6 @@
     <t>201.00</t>
   </si>
   <si>
-    <t>267.00</t>
-  </si>
-  <si>
     <t>147.00</t>
   </si>
   <si>
@@ -1524,48 +1473,21 @@
     <t>179.00</t>
   </si>
   <si>
-    <t>205.00</t>
-  </si>
-  <si>
-    <t>296.00</t>
-  </si>
-  <si>
-    <t>405.00</t>
-  </si>
-  <si>
     <t>221.00</t>
   </si>
   <si>
     <t>148.00</t>
   </si>
   <si>
-    <t>258.00</t>
-  </si>
-  <si>
-    <t>192.00</t>
-  </si>
-  <si>
-    <t>70.00</t>
-  </si>
-  <si>
-    <t>140.00</t>
-  </si>
-  <si>
     <t>121.00</t>
   </si>
   <si>
     <t>42.00</t>
   </si>
   <si>
-    <t>374.00</t>
-  </si>
-  <si>
     <t>48.00</t>
   </si>
   <si>
-    <t>630.00</t>
-  </si>
-  <si>
     <t>160.00</t>
   </si>
   <si>
@@ -1581,30 +1503,15 @@
     <t>36.00</t>
   </si>
   <si>
-    <t>330.00</t>
-  </si>
-  <si>
-    <t>826.00</t>
-  </si>
-  <si>
     <t>2301-22</t>
   </si>
   <si>
     <t>DV CATENA SY-SY 22 6X750 MI</t>
   </si>
   <si>
-    <t>214.00</t>
-  </si>
-  <si>
     <t>35.00</t>
   </si>
   <si>
-    <t>98.00</t>
-  </si>
-  <si>
-    <t>1,127.00</t>
-  </si>
-  <si>
     <t>341-26SC</t>
   </si>
   <si>
@@ -1617,10 +1524,64 @@
     <t>NICASIA VI MB RED BLE 25 6X750</t>
   </si>
   <si>
-    <t>344.00</t>
-  </si>
-  <si>
     <t>154.00</t>
+  </si>
+  <si>
+    <t>101.00</t>
+  </si>
+  <si>
+    <t>328.00</t>
+  </si>
+  <si>
+    <t>204.00</t>
+  </si>
+  <si>
+    <t>295.00</t>
+  </si>
+  <si>
+    <t>404.00</t>
+  </si>
+  <si>
+    <t>265.00</t>
+  </si>
+  <si>
+    <t>781.00</t>
+  </si>
+  <si>
+    <t>183.00</t>
+  </si>
+  <si>
+    <t>212.00</t>
+  </si>
+  <si>
+    <t>243.00</t>
+  </si>
+  <si>
+    <t>65.00</t>
+  </si>
+  <si>
+    <t>138.00</t>
+  </si>
+  <si>
+    <t>1,121.00</t>
+  </si>
+  <si>
+    <t>218.00</t>
+  </si>
+  <si>
+    <t>189.00</t>
+  </si>
+  <si>
+    <t>131.00</t>
+  </si>
+  <si>
+    <t>370.00</t>
+  </si>
+  <si>
+    <t>620.00</t>
+  </si>
+  <si>
+    <t>103.00</t>
   </si>
 </sst>
 </file>
@@ -1972,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC5E5D4-D349-4ED3-89BE-BCC9AFEC568D}">
-  <dimension ref="A1:C222"/>
+  <dimension ref="A1:C216"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -2031,7 +1992,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2042,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>483</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2130,7 +2091,7 @@
         <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2174,7 +2135,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2185,7 +2146,7 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2273,7 +2234,7 @@
         <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2306,7 +2267,7 @@
         <v>51</v>
       </c>
       <c r="C30" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2416,7 +2377,7 @@
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2460,7 +2421,7 @@
         <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2471,7 +2432,7 @@
         <v>85</v>
       </c>
       <c r="C45" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2482,7 +2443,7 @@
         <v>87</v>
       </c>
       <c r="C46" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2526,37 +2487,37 @@
         <v>98</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" t="s">
         <v>100</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>101</v>
-      </c>
-      <c r="C51" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
         <v>103</v>
       </c>
-      <c r="B52" t="s">
-        <v>104</v>
-      </c>
       <c r="C52" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
         <v>105</v>
-      </c>
-      <c r="B53" t="s">
-        <v>106</v>
       </c>
       <c r="C53" t="s">
         <v>23</v>
@@ -2564,409 +2525,409 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" t="s">
         <v>107</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>108</v>
-      </c>
-      <c r="C54" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B55" t="s">
         <v>110</v>
       </c>
-      <c r="B55" t="s">
-        <v>111</v>
-      </c>
       <c r="C55" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
         <v>112</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>113</v>
-      </c>
-      <c r="C56" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
         <v>115</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>116</v>
-      </c>
-      <c r="C57" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58" t="s">
         <v>118</v>
       </c>
-      <c r="B58" t="s">
-        <v>119</v>
-      </c>
       <c r="C58" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" t="s">
         <v>120</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>121</v>
-      </c>
-      <c r="C59" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" t="s">
         <v>123</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>124</v>
-      </c>
-      <c r="C60" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" t="s">
         <v>126</v>
       </c>
-      <c r="B61" t="s">
-        <v>127</v>
-      </c>
       <c r="C61" t="s">
-        <v>128</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>48</v>
+        <v>478</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" t="s">
         <v>131</v>
-      </c>
-      <c r="B63" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" t="s">
         <v>133</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>134</v>
-      </c>
-      <c r="C64" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>135</v>
+      </c>
+      <c r="B65" t="s">
         <v>136</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>137</v>
-      </c>
-      <c r="C65" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>138</v>
+      </c>
+      <c r="B66" t="s">
         <v>139</v>
       </c>
-      <c r="B66" t="s">
-        <v>140</v>
-      </c>
       <c r="C66" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C69" t="s">
-        <v>222</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" t="s">
         <v>150</v>
-      </c>
-      <c r="B71" t="s">
-        <v>151</v>
-      </c>
-      <c r="C71" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
         <v>152</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>153</v>
-      </c>
-      <c r="C72" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>154</v>
+      </c>
+      <c r="B73" t="s">
         <v>155</v>
       </c>
-      <c r="B73" t="s">
-        <v>156</v>
-      </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C74" t="s">
-        <v>63</v>
+        <v>498</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C75" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C76" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C77" t="s">
-        <v>497</v>
+        <v>134</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>166</v>
+      </c>
+      <c r="B79" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" t="s">
         <v>168</v>
-      </c>
-      <c r="B79" t="s">
-        <v>169</v>
-      </c>
-      <c r="C79" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>169</v>
+      </c>
+      <c r="B80" t="s">
         <v>170</v>
       </c>
-      <c r="B80" t="s">
-        <v>171</v>
-      </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C82" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C83" t="s">
-        <v>154</v>
+        <v>480</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B84" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>499</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B85" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C85" t="s">
-        <v>500</v>
+        <v>121</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" t="s">
+        <v>182</v>
+      </c>
+      <c r="C86" t="s">
         <v>183</v>
-      </c>
-      <c r="B86" t="s">
-        <v>184</v>
-      </c>
-      <c r="C86" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" t="s">
         <v>185</v>
       </c>
-      <c r="B87" t="s">
-        <v>186</v>
-      </c>
       <c r="C87" t="s">
-        <v>122</v>
+        <v>502</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" t="s">
         <v>187</v>
       </c>
-      <c r="B88" t="s">
-        <v>188</v>
-      </c>
       <c r="C88" t="s">
-        <v>189</v>
+        <v>25</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" t="s">
         <v>190</v>
-      </c>
-      <c r="B89" t="s">
-        <v>191</v>
-      </c>
-      <c r="C89" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>191</v>
+      </c>
+      <c r="B90" t="s">
         <v>192</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>193</v>
-      </c>
-      <c r="C90" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2977,191 +2938,191 @@
         <v>195</v>
       </c>
       <c r="C91" t="s">
-        <v>196</v>
+        <v>503</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>196</v>
+      </c>
+      <c r="B92" t="s">
         <v>197</v>
       </c>
-      <c r="B92" t="s">
-        <v>198</v>
-      </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C93" t="s">
-        <v>516</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>202</v>
+        <v>470</v>
       </c>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>471</v>
       </c>
       <c r="C94" t="s">
-        <v>485</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C95" t="s">
-        <v>8</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>486</v>
+        <v>203</v>
       </c>
       <c r="B96" t="s">
-        <v>487</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>205</v>
+      </c>
+      <c r="B97" t="s">
         <v>206</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>207</v>
-      </c>
-      <c r="C97" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>208</v>
+      </c>
+      <c r="B98" t="s">
         <v>209</v>
       </c>
-      <c r="B98" t="s">
-        <v>210</v>
-      </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>210</v>
+      </c>
+      <c r="B99" t="s">
         <v>211</v>
       </c>
-      <c r="B99" t="s">
-        <v>212</v>
-      </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>214</v>
+      </c>
+      <c r="B101" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101" t="s">
         <v>216</v>
-      </c>
-      <c r="B101" t="s">
-        <v>217</v>
-      </c>
-      <c r="C101" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>217</v>
+      </c>
+      <c r="B102" t="s">
         <v>218</v>
       </c>
-      <c r="B102" t="s">
-        <v>219</v>
-      </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>219</v>
+      </c>
+      <c r="B103" t="s">
         <v>220</v>
       </c>
-      <c r="B103" t="s">
-        <v>221</v>
-      </c>
       <c r="C103" t="s">
-        <v>222</v>
+        <v>472</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B104" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B105" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C105" t="s">
-        <v>488</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B106" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B107" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>231</v>
+        <v>489</v>
       </c>
       <c r="B108" t="s">
-        <v>232</v>
+        <v>490</v>
       </c>
       <c r="C108" t="s">
         <v>15</v>
@@ -3169,24 +3130,24 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B109" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>231</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>517</v>
+        <v>232</v>
       </c>
       <c r="B110" t="s">
-        <v>518</v>
+        <v>233</v>
       </c>
       <c r="C110" t="s">
-        <v>15</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,51 +3158,51 @@
         <v>236</v>
       </c>
       <c r="C111" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>237</v>
+      </c>
+      <c r="B112" t="s">
         <v>238</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>239</v>
-      </c>
-      <c r="C112" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>240</v>
+      </c>
+      <c r="B113" t="s">
         <v>241</v>
       </c>
-      <c r="B113" t="s">
-        <v>242</v>
-      </c>
       <c r="C113" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>242</v>
+      </c>
+      <c r="B114" t="s">
         <v>243</v>
       </c>
-      <c r="B114" t="s">
-        <v>244</v>
-      </c>
       <c r="C114" t="s">
-        <v>245</v>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>245</v>
+      </c>
+      <c r="B115" t="s">
         <v>246</v>
       </c>
-      <c r="B115" t="s">
-        <v>247</v>
-      </c>
       <c r="C115" t="s">
-        <v>213</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3252,150 +3213,150 @@
         <v>249</v>
       </c>
       <c r="C116" t="s">
-        <v>250</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>250</v>
+      </c>
+      <c r="B117" t="s">
         <v>251</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>252</v>
-      </c>
-      <c r="C117" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>253</v>
+      </c>
+      <c r="B118" t="s">
         <v>254</v>
       </c>
-      <c r="B118" t="s">
-        <v>255</v>
-      </c>
       <c r="C118" t="s">
-        <v>45</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>255</v>
+      </c>
+      <c r="B119" t="s">
         <v>256</v>
       </c>
-      <c r="B119" t="s">
-        <v>257</v>
-      </c>
       <c r="C119" t="s">
-        <v>258</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B120" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>260</v>
+      </c>
+      <c r="B121" t="s">
         <v>261</v>
       </c>
-      <c r="B121" t="s">
-        <v>262</v>
-      </c>
       <c r="C121" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>262</v>
+      </c>
+      <c r="B122" t="s">
         <v>263</v>
       </c>
-      <c r="B122" t="s">
-        <v>264</v>
-      </c>
       <c r="C122" t="s">
-        <v>122</v>
+        <v>505</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>264</v>
+      </c>
+      <c r="B123" t="s">
         <v>265</v>
       </c>
-      <c r="B123" t="s">
-        <v>266</v>
-      </c>
       <c r="C123" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B124" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C124" t="s">
-        <v>213</v>
+        <v>79</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B125" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C125" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B126" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C126" t="s">
-        <v>199</v>
+        <v>244</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B127" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C127" t="s">
-        <v>79</v>
+        <v>507</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" t="s">
         <v>276</v>
       </c>
-      <c r="B128" t="s">
-        <v>277</v>
-      </c>
       <c r="C128" t="s">
-        <v>501</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>277</v>
+      </c>
+      <c r="B129" t="s">
         <v>278</v>
       </c>
-      <c r="B129" t="s">
-        <v>279</v>
-      </c>
       <c r="C129" t="s">
-        <v>502</v>
+        <v>54</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,117 +3367,117 @@
         <v>281</v>
       </c>
       <c r="C130" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>282</v>
+      </c>
+      <c r="B131" t="s">
         <v>283</v>
       </c>
-      <c r="B131" t="s">
-        <v>284</v>
-      </c>
       <c r="C131" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>284</v>
+      </c>
+      <c r="B132" t="s">
         <v>285</v>
       </c>
-      <c r="B132" t="s">
-        <v>286</v>
-      </c>
       <c r="C132" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>286</v>
+      </c>
+      <c r="B133" t="s">
         <v>287</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>288</v>
-      </c>
-      <c r="C133" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" t="s">
         <v>290</v>
       </c>
-      <c r="B134" t="s">
-        <v>291</v>
-      </c>
       <c r="C134" t="s">
-        <v>482</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>291</v>
+      </c>
+      <c r="B135" t="s">
         <v>292</v>
       </c>
-      <c r="B135" t="s">
-        <v>293</v>
-      </c>
       <c r="C135" t="s">
-        <v>114</v>
+        <v>247</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>293</v>
+      </c>
+      <c r="B136" t="s">
         <v>294</v>
       </c>
-      <c r="B136" t="s">
-        <v>295</v>
-      </c>
       <c r="C136" t="s">
-        <v>240</v>
+        <v>113</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
+        <v>295</v>
+      </c>
+      <c r="B137" t="s">
         <v>296</v>
       </c>
-      <c r="B137" t="s">
-        <v>297</v>
-      </c>
       <c r="C137" t="s">
-        <v>298</v>
+        <v>491</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>297</v>
+      </c>
+      <c r="B138" t="s">
+        <v>298</v>
+      </c>
+      <c r="C138" t="s">
         <v>299</v>
-      </c>
-      <c r="B138" t="s">
-        <v>300</v>
-      </c>
-      <c r="C138" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>300</v>
+      </c>
+      <c r="B139" t="s">
         <v>301</v>
       </c>
-      <c r="B139" t="s">
-        <v>302</v>
-      </c>
       <c r="C139" t="s">
-        <v>253</v>
+        <v>487</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>302</v>
+      </c>
+      <c r="B140" t="s">
         <v>303</v>
       </c>
-      <c r="B140" t="s">
+      <c r="C140" t="s">
         <v>304</v>
-      </c>
-      <c r="C140" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3527,18 +3488,18 @@
         <v>306</v>
       </c>
       <c r="C141" t="s">
-        <v>520</v>
+        <v>307</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B142" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C142" t="s">
-        <v>309</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3549,7 +3510,7 @@
         <v>311</v>
       </c>
       <c r="C143" t="s">
-        <v>521</v>
+        <v>113</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3560,95 +3521,95 @@
         <v>313</v>
       </c>
       <c r="C144" t="s">
-        <v>314</v>
+        <v>79</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>314</v>
+      </c>
+      <c r="B145" t="s">
         <v>315</v>
       </c>
-      <c r="B145" t="s">
-        <v>316</v>
-      </c>
       <c r="C145" t="s">
-        <v>317</v>
+        <v>79</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B146" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>508</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B147" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>274</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B148" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C148" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B149" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C149" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>324</v>
+      </c>
+      <c r="B150" t="s">
+        <v>325</v>
+      </c>
+      <c r="C150" t="s">
         <v>326</v>
-      </c>
-      <c r="B150" t="s">
-        <v>327</v>
-      </c>
-      <c r="C150" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>327</v>
+      </c>
+      <c r="B151" t="s">
         <v>328</v>
       </c>
-      <c r="B151" t="s">
-        <v>329</v>
-      </c>
       <c r="C151" t="s">
-        <v>282</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>329</v>
+      </c>
+      <c r="B152" t="s">
         <v>330</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>331</v>
-      </c>
-      <c r="C152" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3659,18 +3620,18 @@
         <v>333</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>481</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B154" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C154" t="s">
-        <v>336</v>
+        <v>414</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3681,7 +3642,7 @@
         <v>338</v>
       </c>
       <c r="C155" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3692,7 +3653,7 @@
         <v>340</v>
       </c>
       <c r="C156" t="s">
-        <v>341</v>
+        <v>134</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3703,304 +3664,304 @@
         <v>343</v>
       </c>
       <c r="C157" t="s">
-        <v>505</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>344</v>
+      </c>
+      <c r="B158" t="s">
         <v>345</v>
       </c>
-      <c r="B158" t="s">
-        <v>346</v>
-      </c>
       <c r="C158" t="s">
-        <v>428</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>346</v>
+      </c>
+      <c r="B159" t="s">
         <v>347</v>
       </c>
-      <c r="B159" t="s">
-        <v>348</v>
-      </c>
       <c r="C159" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>348</v>
+      </c>
+      <c r="B160" t="s">
         <v>349</v>
       </c>
-      <c r="B160" t="s">
-        <v>350</v>
-      </c>
       <c r="C160" t="s">
-        <v>138</v>
+        <v>482</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B161" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C161" t="s">
-        <v>351</v>
+        <v>121</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B162" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C162" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B163" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C163" t="s">
-        <v>25</v>
+        <v>509</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B164" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C164" t="s">
-        <v>506</v>
+        <v>207</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B165" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C165" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B166" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C166" t="s">
-        <v>8</v>
+        <v>207</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>364</v>
+        <v>492</v>
       </c>
       <c r="B167" t="s">
-        <v>365</v>
+        <v>493</v>
       </c>
       <c r="C167" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B168" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C168" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B169" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C169" t="s">
-        <v>172</v>
+        <v>366</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B170" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C170" t="s">
-        <v>213</v>
+        <v>369</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="B171" t="s">
-        <v>524</v>
+        <v>495</v>
       </c>
       <c r="C171" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B172" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C172" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B173" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C173" t="s">
-        <v>376</v>
+        <v>512</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B174" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C174" t="s">
-        <v>379</v>
+        <v>216</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>525</v>
+        <v>376</v>
       </c>
       <c r="B175" t="s">
-        <v>526</v>
+        <v>377</v>
       </c>
       <c r="C175" t="s">
-        <v>527</v>
+        <v>513</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B176" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C176" t="s">
-        <v>15</v>
+        <v>483</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B177" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C177" t="s">
-        <v>28</v>
+        <v>514</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B178" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B179" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C179" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B180" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C180" t="s">
-        <v>507</v>
+        <v>40</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B181" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C181" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B182" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C182" t="s">
-        <v>509</v>
+        <v>207</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>392</v>
+      </c>
+      <c r="B183" t="s">
+        <v>393</v>
+      </c>
+      <c r="C183" t="s">
         <v>394</v>
-      </c>
-      <c r="B183" t="s">
-        <v>395</v>
-      </c>
-      <c r="C183" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>395</v>
+      </c>
+      <c r="B184" t="s">
         <v>396</v>
       </c>
-      <c r="B184" t="s">
+      <c r="C184" t="s">
         <v>397</v>
-      </c>
-      <c r="C184" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,7 +3972,7 @@
         <v>399</v>
       </c>
       <c r="C185" t="s">
-        <v>40</v>
+        <v>369</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4022,7 +3983,7 @@
         <v>401</v>
       </c>
       <c r="C186" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,29 +3994,29 @@
         <v>403</v>
       </c>
       <c r="C187" t="s">
-        <v>213</v>
+        <v>404</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B188" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C188" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B189" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C189" t="s">
-        <v>409</v>
+        <v>69</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,7 +4027,7 @@
         <v>411</v>
       </c>
       <c r="C190" t="s">
-        <v>379</v>
+        <v>473</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4077,18 +4038,18 @@
         <v>413</v>
       </c>
       <c r="C191" t="s">
-        <v>99</v>
+        <v>414</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B192" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C192" t="s">
-        <v>416</v>
+        <v>28</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4099,7 +4060,7 @@
         <v>418</v>
       </c>
       <c r="C193" t="s">
-        <v>8</v>
+        <v>484</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4110,172 +4071,172 @@
         <v>420</v>
       </c>
       <c r="C194" t="s">
-        <v>421</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>421</v>
+      </c>
+      <c r="B195" t="s">
         <v>422</v>
       </c>
-      <c r="B195" t="s">
-        <v>423</v>
-      </c>
       <c r="C195" t="s">
-        <v>69</v>
+        <v>478</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>423</v>
+      </c>
+      <c r="B196" t="s">
         <v>424</v>
       </c>
-      <c r="B196" t="s">
-        <v>425</v>
-      </c>
       <c r="C196" t="s">
-        <v>490</v>
+        <v>37</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" t="s">
         <v>426</v>
       </c>
-      <c r="B197" t="s">
-        <v>427</v>
-      </c>
       <c r="C197" t="s">
-        <v>428</v>
+        <v>480</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B198" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C198" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B199" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C199" t="s">
-        <v>510</v>
+        <v>274</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B200" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C200" t="s">
-        <v>471</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B201" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C201" t="s">
-        <v>495</v>
+        <v>121</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B202" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C202" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B203" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C203" t="s">
-        <v>500</v>
+        <v>121</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B204" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C204" t="s">
-        <v>13</v>
+        <v>190</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
+        <v>441</v>
+      </c>
+      <c r="B205" t="s">
+        <v>442</v>
+      </c>
+      <c r="C205" t="s">
         <v>443</v>
-      </c>
-      <c r="B205" t="s">
-        <v>444</v>
-      </c>
-      <c r="C205" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>444</v>
+      </c>
+      <c r="B206" t="s">
         <v>445</v>
       </c>
-      <c r="B206" t="s">
-        <v>446</v>
-      </c>
       <c r="C206" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
+        <v>446</v>
+      </c>
+      <c r="B207" t="s">
         <v>447</v>
       </c>
-      <c r="B207" t="s">
-        <v>448</v>
-      </c>
       <c r="C207" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
+        <v>448</v>
+      </c>
+      <c r="B208" t="s">
         <v>449</v>
       </c>
-      <c r="B208" t="s">
-        <v>450</v>
-      </c>
       <c r="C208" t="s">
-        <v>213</v>
+        <v>23</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>450</v>
+      </c>
+      <c r="B209" t="s">
         <v>451</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>452</v>
-      </c>
-      <c r="C209" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4286,7 +4247,7 @@
         <v>454</v>
       </c>
       <c r="C210" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4308,7 +4269,7 @@
         <v>459</v>
       </c>
       <c r="C212" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4319,7 +4280,7 @@
         <v>461</v>
       </c>
       <c r="C213" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4330,7 +4291,7 @@
         <v>463</v>
       </c>
       <c r="C214" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4341,83 +4302,17 @@
         <v>465</v>
       </c>
       <c r="C215" t="s">
-        <v>466</v>
+        <v>15</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" t="s">
         <v>467</v>
       </c>
-      <c r="B216" t="s">
-        <v>468</v>
-      </c>
       <c r="C216" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>469</v>
-      </c>
-      <c r="B217" t="s">
-        <v>470</v>
-      </c>
-      <c r="C217" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>472</v>
-      </c>
-      <c r="B218" t="s">
-        <v>473</v>
-      </c>
-      <c r="C218" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>474</v>
-      </c>
-      <c r="B219" t="s">
-        <v>475</v>
-      </c>
-      <c r="C219" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>476</v>
-      </c>
-      <c r="B220" t="s">
-        <v>477</v>
-      </c>
-      <c r="C220" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>478</v>
-      </c>
-      <c r="B221" t="s">
-        <v>479</v>
-      </c>
-      <c r="C221" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>480</v>
-      </c>
-      <c r="B222" t="s">
-        <v>481</v>
-      </c>
-      <c r="C222" t="s">
         <v>25</v>
       </c>
     </row>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariano\Desktop\stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003E0273-5071-42BD-9E5F-C62BBC0B32C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C245C8D-EDF2-4EF0-8468-BA1CEF6E7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EE8A0F23-18C3-4A4D-8D5C-85AD26929363}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="522">
   <si>
     <t>Producto</t>
   </si>
@@ -54,9 +54,6 @@
     <t>ESTIBA I CAB-SAUV 6X750</t>
   </si>
   <si>
-    <t>ESTIBA I CHARDONNAY 6X750</t>
-  </si>
-  <si>
     <t>4.00</t>
   </si>
   <si>
@@ -219,9 +216,6 @@
     <t>CAT CHAR. APPEL. TUP 24 6X750</t>
   </si>
   <si>
-    <t>102.00</t>
-  </si>
-  <si>
     <t>1173-24</t>
   </si>
   <si>
@@ -933,9 +927,6 @@
     <t>CAT MB.APP.LUNLUNTA 24 6X75</t>
   </si>
   <si>
-    <t>109.00</t>
-  </si>
-  <si>
     <t>2881-22</t>
   </si>
   <si>
@@ -1359,9 +1350,6 @@
     <t>48.00</t>
   </si>
   <si>
-    <t>160.00</t>
-  </si>
-  <si>
     <t>63.00</t>
   </si>
   <si>
@@ -1392,9 +1380,6 @@
     <t>NICASIA VI MB RED BLE 25 6X750</t>
   </si>
   <si>
-    <t>154.00</t>
-  </si>
-  <si>
     <t>101.00</t>
   </si>
   <si>
@@ -1404,12 +1389,6 @@
     <t>183.00</t>
   </si>
   <si>
-    <t>138.00</t>
-  </si>
-  <si>
-    <t>620.00</t>
-  </si>
-  <si>
     <t>103.00</t>
   </si>
   <si>
@@ -1422,9 +1401,6 @@
     <t>268.00</t>
   </si>
   <si>
-    <t>329.00</t>
-  </si>
-  <si>
     <t>202.00</t>
   </si>
   <si>
@@ -1434,21 +1410,12 @@
     <t>267.00</t>
   </si>
   <si>
-    <t>759.00</t>
-  </si>
-  <si>
     <t>162.00</t>
   </si>
   <si>
     <t>167.00</t>
   </si>
   <si>
-    <t>422.00</t>
-  </si>
-  <si>
-    <t>210.00</t>
-  </si>
-  <si>
     <t>2381-24</t>
   </si>
   <si>
@@ -1461,45 +1428,18 @@
     <t>DV TTO HIST PARAJ 24 4X75 TERR</t>
   </si>
   <si>
-    <t>234.00</t>
-  </si>
-  <si>
-    <t>185.00</t>
-  </si>
-  <si>
     <t>2545-25</t>
   </si>
   <si>
     <t>SF MALBEC 25 6X750 B/ELIT</t>
   </si>
   <si>
-    <t>465.00</t>
-  </si>
-  <si>
-    <t>126.00</t>
-  </si>
-  <si>
-    <t>1,088.00</t>
-  </si>
-  <si>
-    <t>41.00</t>
-  </si>
-  <si>
-    <t>207.00</t>
-  </si>
-  <si>
-    <t>16.00</t>
-  </si>
-  <si>
     <t>421-25MI</t>
   </si>
   <si>
     <t>NICASIA VINE CS-FR 25 6X750</t>
   </si>
   <si>
-    <t>242.00</t>
-  </si>
-  <si>
     <t>588.00</t>
   </si>
   <si>
@@ -1509,10 +1449,157 @@
     <t>EL ENEMIGO CF 23 6X75 MI</t>
   </si>
   <si>
-    <t>104.00</t>
-  </si>
-  <si>
-    <t>141.00</t>
+    <t>87.00</t>
+  </si>
+  <si>
+    <t>98.00</t>
+  </si>
+  <si>
+    <t>327.00</t>
+  </si>
+  <si>
+    <t>752.00</t>
+  </si>
+  <si>
+    <t>395.00</t>
+  </si>
+  <si>
+    <t>204.00</t>
+  </si>
+  <si>
+    <t>223.00</t>
+  </si>
+  <si>
+    <t>451.00</t>
+  </si>
+  <si>
+    <t>106.00</t>
+  </si>
+  <si>
+    <t>137.00</t>
+  </si>
+  <si>
+    <t>180.00</t>
+  </si>
+  <si>
+    <t>1,035.00</t>
+  </si>
+  <si>
+    <t>84.00</t>
+  </si>
+  <si>
+    <t>618.00</t>
+  </si>
+  <si>
+    <t>73.00</t>
+  </si>
+  <si>
+    <t>153.00</t>
+  </si>
+  <si>
+    <t>139.00</t>
+  </si>
+  <si>
+    <t>MK04-11</t>
+  </si>
+  <si>
+    <t>COPON LOGO CATENA ZAPATA X12</t>
+  </si>
+  <si>
+    <t>MK04-14</t>
+  </si>
+  <si>
+    <t>COPON LOGO SAINT FELICIEN X12</t>
+  </si>
+  <si>
+    <t>MK05-04</t>
+  </si>
+  <si>
+    <t>FRAPERAS CHICAS ESMERALDA</t>
+  </si>
+  <si>
+    <t>MK05-05</t>
+  </si>
+  <si>
+    <t>FRAPERA NICASIA</t>
+  </si>
+  <si>
+    <t>MK05-06</t>
+  </si>
+  <si>
+    <t>FRAPERA SAINT FELICIEN</t>
+  </si>
+  <si>
+    <t>24.00</t>
+  </si>
+  <si>
+    <t>MK05-08</t>
+  </si>
+  <si>
+    <t>CANASTITO NICASIA</t>
+  </si>
+  <si>
+    <t>MK05-16</t>
+  </si>
+  <si>
+    <t>CANASTITO TILIA ORGANICO</t>
+  </si>
+  <si>
+    <t>MK08-01</t>
+  </si>
+  <si>
+    <t>SACARCORCHOS UXMAL</t>
+  </si>
+  <si>
+    <t>299.00</t>
+  </si>
+  <si>
+    <t>MK08-03</t>
+  </si>
+  <si>
+    <t>SACACORCHO SAINT FELICIEN</t>
+  </si>
+  <si>
+    <t>MK08-04</t>
+  </si>
+  <si>
+    <t>SACACORCHOS ALAMOS</t>
+  </si>
+  <si>
+    <t>135.00</t>
+  </si>
+  <si>
+    <t>MK08-06</t>
+  </si>
+  <si>
+    <t>SACACORCHO LOGO NICASIA</t>
+  </si>
+  <si>
+    <t>229.00</t>
+  </si>
+  <si>
+    <t>MK10-04</t>
+  </si>
+  <si>
+    <t>BASE ALAMOS</t>
+  </si>
+  <si>
+    <t>MK10-16</t>
+  </si>
+  <si>
+    <t>EXHIBIDOR TORRE NICASIA</t>
+  </si>
+  <si>
+    <t>MK11-03</t>
+  </si>
+  <si>
+    <t>CHAPA NICASIA</t>
+  </si>
+  <si>
+    <t>MK15-01</t>
+  </si>
+  <si>
+    <t>CUADRO ALAMOS MADERA</t>
   </si>
 </sst>
 </file>
@@ -1864,7 +1951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC5E5D4-D349-4ED3-89BE-BCC9AFEC568D}">
-  <dimension ref="A1:C203"/>
+  <dimension ref="A1:C217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -1883,2225 +1970,2379 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>186</v>
+      <c r="A2" t="s">
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>360</v>
+      <c r="A3" t="s">
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>459</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>370</v>
+      <c r="A4" t="s">
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>375</v>
+      <c r="A5" t="s">
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>326</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>428</v>
+      <c r="A6" t="s">
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>269</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>442</v>
+      <c r="A7" t="s">
+        <v>70</v>
       </c>
       <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>452</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>453</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>454</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>456</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>457</v>
-      </c>
-      <c r="B12" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" t="s">
         <v>21</v>
       </c>
-      <c r="C12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>458</v>
-      </c>
-      <c r="B13" t="s">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>124</v>
+      </c>
+      <c r="C28" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>134</v>
+      </c>
+      <c r="B32" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>459</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>460</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>461</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>526</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>527</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>528</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>585</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>586</v>
-      </c>
-      <c r="B21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>587</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>1902</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>1905</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>1915</v>
-      </c>
-      <c r="B25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>1917</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>1927</v>
-      </c>
-      <c r="B27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>1928</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>1956</v>
-      </c>
-      <c r="B29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>1957</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>1959</v>
-      </c>
-      <c r="B31" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2061</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" t="s">
-        <v>460</v>
-      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2271</v>
+      <c r="A33" t="s">
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>2390</v>
+      <c r="A34" t="s">
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>140</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>145</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>473</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>154</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="C43" t="s">
-        <v>461</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="C44" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="C45" t="s">
-        <v>444</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>87</v>
+      <c r="A46">
+        <v>186</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>90</v>
+      <c r="A47">
+        <v>1902</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>92</v>
+      <c r="A48">
+        <v>1905</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="C48" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>95</v>
+      <c r="A49">
+        <v>1915</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C49" t="s">
-        <v>453</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>97</v>
+      <c r="A50">
+        <v>1917</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="C50" t="s">
-        <v>99</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>100</v>
+      <c r="A51">
+        <v>1927</v>
       </c>
       <c r="B51" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="C51" t="s">
-        <v>427</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>102</v>
+      <c r="A52">
+        <v>1928</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>104</v>
+      <c r="A53">
+        <v>1956</v>
       </c>
       <c r="B53" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="C53" t="s">
-        <v>106</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>107</v>
+      <c r="A54">
+        <v>1957</v>
       </c>
       <c r="B54" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="C54" t="s">
-        <v>434</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>109</v>
+      <c r="A55">
+        <v>1959</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>165</v>
       </c>
       <c r="B56" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>167</v>
       </c>
       <c r="B57" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="C57" t="s">
-        <v>435</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>117</v>
+      <c r="A58">
+        <v>2061</v>
       </c>
       <c r="B58" t="s">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="C58" t="s">
-        <v>119</v>
+        <v>453</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="B59" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C60" t="s">
-        <v>46</v>
+        <v>435</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="C61" t="s">
-        <v>436</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="C64" t="s">
-        <v>135</v>
+        <v>457</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="C66" t="s">
-        <v>135</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="B67" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>474</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>425</v>
       </c>
       <c r="B71" t="s">
-        <v>150</v>
+        <v>426</v>
       </c>
       <c r="C71" t="s">
-        <v>151</v>
+        <v>434</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>462</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="B74" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>463</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="C75" t="s">
-        <v>454</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>208</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>164</v>
+      <c r="A78">
+        <v>2271</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="C78" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="C79" t="s">
-        <v>464</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>214</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="B81" t="s">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="C81" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="C82" t="s">
-        <v>438</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="B83" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="C83" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="C84" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>180</v>
+        <v>224</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>182</v>
+        <v>441</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>442</v>
       </c>
       <c r="C86" t="s">
-        <v>465</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="B87" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>227</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="B88" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="C88" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="B89" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="C89" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
       <c r="C90" t="s">
-        <v>466</v>
+        <v>235</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="C91" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
+        <v>433</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>428</v>
+        <v>240</v>
       </c>
       <c r="B93" t="s">
-        <v>429</v>
+        <v>241</v>
       </c>
       <c r="C93" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="B94" t="s">
-        <v>199</v>
+        <v>244</v>
       </c>
       <c r="C94" t="s">
-        <v>200</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="B95" t="s">
-        <v>202</v>
+        <v>246</v>
       </c>
       <c r="C95" t="s">
-        <v>27</v>
+        <v>459</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>247</v>
+      </c>
+      <c r="B96" t="s">
+        <v>248</v>
+      </c>
+      <c r="C96" t="s">
         <v>203</v>
-      </c>
-      <c r="B96" t="s">
-        <v>204</v>
-      </c>
-      <c r="C96" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="C97" t="s">
-        <v>205</v>
+        <v>475</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="B98" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="C98" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>212</v>
+        <v>255</v>
       </c>
       <c r="B100" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
       <c r="C100" t="s">
-        <v>214</v>
+        <v>476</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="B101" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="C101" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>217</v>
+        <v>460</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>461</v>
       </c>
       <c r="C102" t="s">
-        <v>430</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>462</v>
       </c>
       <c r="B103" t="s">
-        <v>220</v>
+        <v>463</v>
       </c>
       <c r="C103" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>221</v>
+      <c r="A104">
+        <v>2390</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="B105" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="C105" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="B106" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>477</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>445</v>
+        <v>263</v>
       </c>
       <c r="B107" t="s">
-        <v>446</v>
+        <v>264</v>
       </c>
       <c r="C107" t="s">
-        <v>14</v>
+        <v>450</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>266</v>
       </c>
       <c r="C108" t="s">
-        <v>229</v>
+        <v>438</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>464</v>
       </c>
       <c r="B109" t="s">
-        <v>231</v>
+        <v>465</v>
       </c>
       <c r="C109" t="s">
-        <v>232</v>
+        <v>478</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>233</v>
+        <v>268</v>
       </c>
       <c r="B110" t="s">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="C110" t="s">
-        <v>232</v>
+        <v>479</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>235</v>
+        <v>270</v>
       </c>
       <c r="B111" t="s">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="C111" t="s">
-        <v>237</v>
+        <v>443</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
       <c r="B112" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="C112" t="s">
-        <v>205</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
       <c r="B113" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="C113" t="s">
-        <v>455</v>
+        <v>230</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
       <c r="B114" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="C114" t="s">
-        <v>467</v>
+        <v>278</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>245</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>246</v>
+        <v>284</v>
       </c>
       <c r="C115" t="s">
-        <v>43</v>
+        <v>394</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>247</v>
+        <v>279</v>
       </c>
       <c r="B116" t="s">
-        <v>248</v>
+        <v>280</v>
       </c>
       <c r="C116" t="s">
-        <v>468</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="C117" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="C118" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="C119" t="s">
-        <v>77</v>
+        <v>289</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="C120" t="s">
-        <v>205</v>
+        <v>439</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="B121" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="C121" t="s">
-        <v>470</v>
+        <v>294</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="B122" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="C122" t="s">
-        <v>166</v>
+        <v>452</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>471</v>
+        <v>299</v>
       </c>
       <c r="B123" t="s">
-        <v>472</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
-        <v>32</v>
+        <v>109</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>473</v>
+        <v>301</v>
       </c>
       <c r="B124" t="s">
-        <v>474</v>
+        <v>302</v>
       </c>
       <c r="C124" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="B125" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="C125" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="B126" t="s">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="C126" t="s">
-        <v>475</v>
+        <v>75</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="B127" t="s">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="C127" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>307</v>
+      </c>
+      <c r="B128" t="s">
+        <v>308</v>
+      </c>
+      <c r="C128" t="s">
         <v>267</v>
-      </c>
-      <c r="B128" t="s">
-        <v>268</v>
-      </c>
-      <c r="C128" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>477</v>
+        <v>309</v>
       </c>
       <c r="B129" t="s">
-        <v>478</v>
+        <v>310</v>
       </c>
       <c r="C129" t="s">
-        <v>479</v>
+        <v>436</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="B130" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
       <c r="C130" t="s">
-        <v>459</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="B131" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="C131" t="s">
-        <v>447</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="B132" t="s">
-        <v>275</v>
+        <v>317</v>
       </c>
       <c r="C132" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="C133" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>278</v>
+        <v>321</v>
       </c>
       <c r="B134" t="s">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="C134" t="s">
-        <v>280</v>
+        <v>436</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="B135" t="s">
-        <v>282</v>
+        <v>325</v>
       </c>
       <c r="C135" t="s">
-        <v>205</v>
+        <v>481</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>283</v>
+        <v>331</v>
       </c>
       <c r="B136" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="C136" t="s">
-        <v>244</v>
+        <v>330</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
       <c r="B137" t="s">
-        <v>286</v>
+        <v>327</v>
       </c>
       <c r="C137" t="s">
-        <v>397</v>
+        <v>84</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="B138" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
       <c r="C138" t="s">
-        <v>447</v>
+        <v>130</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="B139" t="s">
-        <v>290</v>
+        <v>334</v>
       </c>
       <c r="C139" t="s">
-        <v>291</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>292</v>
+        <v>335</v>
       </c>
       <c r="B140" t="s">
-        <v>293</v>
+        <v>336</v>
       </c>
       <c r="C140" t="s">
-        <v>443</v>
+        <v>23</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="B141" t="s">
-        <v>295</v>
+        <v>338</v>
       </c>
       <c r="C141" t="s">
-        <v>296</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>297</v>
+        <v>339</v>
       </c>
       <c r="B142" t="s">
-        <v>298</v>
+        <v>340</v>
       </c>
       <c r="C142" t="s">
-        <v>299</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="B143" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="C143" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>302</v>
+        <v>343</v>
       </c>
       <c r="B144" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="C144" t="s">
-        <v>111</v>
+        <v>482</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="B145" t="s">
-        <v>305</v>
+        <v>346</v>
       </c>
       <c r="C145" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>306</v>
+        <v>347</v>
       </c>
       <c r="B146" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="C146" t="s">
-        <v>77</v>
+        <v>320</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="B147" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="C147" t="s">
-        <v>456</v>
+        <v>203</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>310</v>
+        <v>444</v>
       </c>
       <c r="B148" t="s">
-        <v>311</v>
+        <v>445</v>
       </c>
       <c r="C148" t="s">
-        <v>269</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>312</v>
+      <c r="A149">
+        <v>360</v>
       </c>
       <c r="B149" t="s">
-        <v>313</v>
+        <v>5</v>
       </c>
       <c r="C149" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>314</v>
+      <c r="A150">
+        <v>375</v>
       </c>
       <c r="B150" t="s">
-        <v>315</v>
+        <v>7</v>
       </c>
       <c r="C150" t="s">
-        <v>12</v>
+        <v>323</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="B151" t="s">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="C151" t="s">
-        <v>318</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>319</v>
+        <v>353</v>
       </c>
       <c r="B152" t="s">
-        <v>320</v>
+        <v>354</v>
       </c>
       <c r="C152" t="s">
-        <v>14</v>
+        <v>355</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>321</v>
+        <v>446</v>
       </c>
       <c r="B153" t="s">
-        <v>322</v>
+        <v>447</v>
       </c>
       <c r="C153" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
       <c r="B154" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="C154" t="s">
-        <v>439</v>
+        <v>358</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>327</v>
+        <v>466</v>
       </c>
       <c r="B155" t="s">
-        <v>328</v>
+        <v>467</v>
       </c>
       <c r="C155" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="B156" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="C156" t="s">
-        <v>86</v>
+        <v>483</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="B157" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="C157" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="B158" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="C158" t="s">
-        <v>333</v>
+        <v>468</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>336</v>
+      <c r="A159">
+        <v>428</v>
       </c>
       <c r="B159" t="s">
-        <v>337</v>
+        <v>8</v>
       </c>
       <c r="C159" t="s">
-        <v>77</v>
+        <v>227</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="B160" t="s">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="C160" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>442</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>452</v>
+      </c>
+      <c r="B162" t="s">
+        <v>12</v>
+      </c>
+      <c r="C162" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>453</v>
+      </c>
+      <c r="B163" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>454</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>456</v>
+      </c>
+      <c r="B165" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>457</v>
+      </c>
+      <c r="B166" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>458</v>
+      </c>
+      <c r="B167" t="s">
+        <v>22</v>
+      </c>
+      <c r="C167" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>459</v>
+      </c>
+      <c r="B168" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>340</v>
-      </c>
-      <c r="B161" t="s">
-        <v>341</v>
-      </c>
-      <c r="C161" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>342</v>
-      </c>
-      <c r="B162" t="s">
-        <v>343</v>
-      </c>
-      <c r="C162" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>344</v>
-      </c>
-      <c r="B163" t="s">
-        <v>345</v>
-      </c>
-      <c r="C163" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>346</v>
-      </c>
-      <c r="B164" t="s">
-        <v>347</v>
-      </c>
-      <c r="C164" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>348</v>
-      </c>
-      <c r="B165" t="s">
-        <v>349</v>
-      </c>
-      <c r="C165" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>350</v>
-      </c>
-      <c r="B166" t="s">
-        <v>351</v>
-      </c>
-      <c r="C166" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>352</v>
-      </c>
-      <c r="B167" t="s">
-        <v>353</v>
-      </c>
-      <c r="C167" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>448</v>
-      </c>
-      <c r="B168" t="s">
-        <v>449</v>
-      </c>
       <c r="C168" t="s">
-        <v>483</v>
+        <v>355</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>354</v>
+      <c r="A169">
+        <v>460</v>
       </c>
       <c r="B169" t="s">
-        <v>355</v>
+        <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>24</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>356</v>
+      <c r="A170">
+        <v>461</v>
       </c>
       <c r="B170" t="s">
-        <v>357</v>
+        <v>27</v>
       </c>
       <c r="C170" t="s">
-        <v>358</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B171" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C171" t="s">
-        <v>361</v>
+        <v>484</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>450</v>
+        <v>369</v>
       </c>
       <c r="B172" t="s">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="C172" t="s">
-        <v>484</v>
+        <v>31</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="B173" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C173" t="s">
-        <v>148</v>
+        <v>485</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>485</v>
+        <v>373</v>
       </c>
       <c r="B174" t="s">
-        <v>486</v>
+        <v>374</v>
       </c>
       <c r="C174" t="s">
-        <v>487</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B175" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C175" t="s">
-        <v>214</v>
+        <v>486</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B176" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="C176" t="s">
-        <v>488</v>
+        <v>203</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="B177" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="C177" t="s">
-        <v>440</v>
+        <v>381</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="B178" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C178" t="s">
-        <v>457</v>
+        <v>384</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B179" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="C179" t="s">
-        <v>32</v>
+        <v>358</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="B180" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="C180" t="s">
-        <v>229</v>
+        <v>451</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="B181" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="C181" t="s">
-        <v>39</v>
+        <v>391</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>378</v>
+        <v>469</v>
       </c>
       <c r="B182" t="s">
-        <v>379</v>
+        <v>470</v>
       </c>
       <c r="C182" t="s">
-        <v>452</v>
+        <v>133</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B183" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C183" t="s">
-        <v>205</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="B184" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="C184" t="s">
-        <v>384</v>
+        <v>65</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B185" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C185" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="B186" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C186" t="s">
-        <v>361</v>
+        <v>487</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="B187" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="C187" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B188" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C188" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>489</v>
+        <v>402</v>
       </c>
       <c r="B189" t="s">
-        <v>490</v>
+        <v>403</v>
       </c>
       <c r="C189" t="s">
-        <v>491</v>
+        <v>26</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="B190" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="C190" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B191" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C191" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B192" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C192" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>402</v>
+      <c r="A193">
+        <v>526</v>
       </c>
       <c r="B193" t="s">
-        <v>403</v>
+        <v>29</v>
       </c>
       <c r="C193" t="s">
-        <v>404</v>
+        <v>62</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>405</v>
+      <c r="A194">
+        <v>527</v>
       </c>
       <c r="B194" t="s">
-        <v>406</v>
+        <v>30</v>
       </c>
       <c r="C194" t="s">
-        <v>27</v>
+        <v>422</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>407</v>
+      <c r="A195">
+        <v>528</v>
       </c>
       <c r="B195" t="s">
-        <v>408</v>
+        <v>32</v>
       </c>
       <c r="C195" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>409</v>
+      <c r="A196">
+        <v>585</v>
       </c>
       <c r="B196" t="s">
-        <v>410</v>
+        <v>33</v>
       </c>
       <c r="C196" t="s">
-        <v>492</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>411</v>
+      <c r="A197">
+        <v>586</v>
       </c>
       <c r="B197" t="s">
-        <v>412</v>
+        <v>34</v>
       </c>
       <c r="C197" t="s">
-        <v>436</v>
+        <v>35</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>413</v>
+      <c r="A198">
+        <v>587</v>
       </c>
       <c r="B198" t="s">
-        <v>414</v>
+        <v>36</v>
       </c>
       <c r="C198" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>414</v>
+      </c>
+      <c r="B199" t="s">
         <v>415</v>
       </c>
-      <c r="B199" t="s">
-        <v>416</v>
-      </c>
       <c r="C199" t="s">
-        <v>438</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>416</v>
+      </c>
+      <c r="B200" t="s">
         <v>417</v>
       </c>
-      <c r="B200" t="s">
-        <v>418</v>
-      </c>
       <c r="C200" t="s">
-        <v>12</v>
+        <v>267</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
+        <v>418</v>
+      </c>
+      <c r="B201" t="s">
         <v>419</v>
       </c>
-      <c r="B201" t="s">
-        <v>420</v>
-      </c>
       <c r="C201" t="s">
-        <v>269</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>420</v>
+      </c>
+      <c r="B202" t="s">
         <v>421</v>
       </c>
-      <c r="B202" t="s">
-        <v>422</v>
-      </c>
       <c r="C202" t="s">
-        <v>12</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>423</v>
+        <v>488</v>
       </c>
       <c r="B203" t="s">
-        <v>424</v>
+        <v>489</v>
       </c>
       <c r="C203" t="s">
-        <v>119</v>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>490</v>
+      </c>
+      <c r="B204" t="s">
+        <v>491</v>
+      </c>
+      <c r="C204" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>492</v>
+      </c>
+      <c r="B205" t="s">
+        <v>493</v>
+      </c>
+      <c r="C205" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>494</v>
+      </c>
+      <c r="B206" t="s">
+        <v>495</v>
+      </c>
+      <c r="C206" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>496</v>
+      </c>
+      <c r="B207" t="s">
+        <v>497</v>
+      </c>
+      <c r="C207" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>499</v>
+      </c>
+      <c r="B208" t="s">
+        <v>500</v>
+      </c>
+      <c r="C208" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>501</v>
+      </c>
+      <c r="B209" t="s">
+        <v>502</v>
+      </c>
+      <c r="C209" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>503</v>
+      </c>
+      <c r="B210" t="s">
+        <v>504</v>
+      </c>
+      <c r="C210" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>506</v>
+      </c>
+      <c r="B211" t="s">
+        <v>507</v>
+      </c>
+      <c r="C211" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>508</v>
+      </c>
+      <c r="B212" t="s">
+        <v>509</v>
+      </c>
+      <c r="C212" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>511</v>
+      </c>
+      <c r="B213" t="s">
+        <v>512</v>
+      </c>
+      <c r="C213" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>514</v>
+      </c>
+      <c r="B214" t="s">
+        <v>515</v>
+      </c>
+      <c r="C214" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>516</v>
+      </c>
+      <c r="B215" t="s">
+        <v>517</v>
+      </c>
+      <c r="C215" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>518</v>
+      </c>
+      <c r="B216" t="s">
+        <v>519</v>
+      </c>
+      <c r="C216" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>520</v>
+      </c>
+      <c r="B217" t="s">
+        <v>521</v>
+      </c>
+      <c r="C217" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mariano\Desktop\stock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C245C8D-EDF2-4EF0-8468-BA1CEF6E7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310FDD20-44F4-4A20-A1CC-7A665AD0A018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EE8A0F23-18C3-4A4D-8D5C-85AD26929363}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="529">
   <si>
     <t>Producto</t>
   </si>
@@ -297,9 +297,6 @@
     <t>PADRILLOS ROSADO 25 6X750 SC</t>
   </si>
   <si>
-    <t>114.00</t>
-  </si>
-  <si>
     <t>1339-22</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
     <t>TIKAL CORAZON EL CEP 21 6X750</t>
   </si>
   <si>
-    <t>29.00</t>
-  </si>
-  <si>
     <t>1489-21</t>
   </si>
   <si>
@@ -870,9 +864,6 @@
     <t>SAINT FEL FUME BLANC 24 6X75</t>
   </si>
   <si>
-    <t>336.00</t>
-  </si>
-  <si>
     <t>2673-25</t>
   </si>
   <si>
@@ -1059,12 +1050,6 @@
     <t>ALAMOS WOTM MAC AT 25 6X750 SC</t>
   </si>
   <si>
-    <t>3230-25</t>
-  </si>
-  <si>
-    <t>ALAMOS WOTM MB 25 12X375 MI</t>
-  </si>
-  <si>
     <t>330-25</t>
   </si>
   <si>
@@ -1083,12 +1068,6 @@
     <t>ALAMOS CB SV WOTM 24 6X750</t>
   </si>
   <si>
-    <t>3392-NV</t>
-  </si>
-  <si>
-    <t>ALAMOS WOTM DULCE NAT 6X750</t>
-  </si>
-  <si>
     <t>3820-17</t>
   </si>
   <si>
@@ -1308,9 +1287,6 @@
     <t>78.00</t>
   </si>
   <si>
-    <t>10.00</t>
-  </si>
-  <si>
     <t>2212-23</t>
   </si>
   <si>
@@ -1356,9 +1332,6 @@
     <t>95.00</t>
   </si>
   <si>
-    <t>36.00</t>
-  </si>
-  <si>
     <t>2301-22</t>
   </si>
   <si>
@@ -1386,9 +1359,6 @@
     <t>295.00</t>
   </si>
   <si>
-    <t>183.00</t>
-  </si>
-  <si>
     <t>103.00</t>
   </si>
   <si>
@@ -1398,24 +1368,9 @@
     <t>58.00</t>
   </si>
   <si>
-    <t>268.00</t>
-  </si>
-  <si>
-    <t>202.00</t>
-  </si>
-  <si>
-    <t>407.00</t>
-  </si>
-  <si>
     <t>267.00</t>
   </si>
   <si>
-    <t>162.00</t>
-  </si>
-  <si>
-    <t>167.00</t>
-  </si>
-  <si>
     <t>2381-24</t>
   </si>
   <si>
@@ -1440,9 +1395,6 @@
     <t>NICASIA VINE CS-FR 25 6X750</t>
   </si>
   <si>
-    <t>588.00</t>
-  </si>
-  <si>
     <t>493-23</t>
   </si>
   <si>
@@ -1455,51 +1407,21 @@
     <t>98.00</t>
   </si>
   <si>
-    <t>327.00</t>
-  </si>
-  <si>
-    <t>752.00</t>
-  </si>
-  <si>
-    <t>395.00</t>
-  </si>
-  <si>
-    <t>204.00</t>
-  </si>
-  <si>
-    <t>223.00</t>
-  </si>
-  <si>
-    <t>451.00</t>
-  </si>
-  <si>
     <t>106.00</t>
   </si>
   <si>
-    <t>137.00</t>
-  </si>
-  <si>
     <t>180.00</t>
   </si>
   <si>
-    <t>1,035.00</t>
-  </si>
-  <si>
     <t>84.00</t>
   </si>
   <si>
-    <t>618.00</t>
-  </si>
-  <si>
     <t>73.00</t>
   </si>
   <si>
     <t>153.00</t>
   </si>
   <si>
-    <t>139.00</t>
-  </si>
-  <si>
     <t>MK04-11</t>
   </si>
   <si>
@@ -1600,6 +1522,105 @@
   </si>
   <si>
     <t>CUADRO ALAMOS MADERA</t>
+  </si>
+  <si>
+    <t>122.00</t>
+  </si>
+  <si>
+    <t>265.00</t>
+  </si>
+  <si>
+    <t>112.00</t>
+  </si>
+  <si>
+    <t>99.00</t>
+  </si>
+  <si>
+    <t>82.00</t>
+  </si>
+  <si>
+    <t>324.00</t>
+  </si>
+  <si>
+    <t>200.00</t>
+  </si>
+  <si>
+    <t>404.00</t>
+  </si>
+  <si>
+    <t>219.00</t>
+  </si>
+  <si>
+    <t>698.00</t>
+  </si>
+  <si>
+    <t>2330-22</t>
+  </si>
+  <si>
+    <t>DV CHARD-CHARD 22 6X750 MI</t>
+  </si>
+  <si>
+    <t>155.00</t>
+  </si>
+  <si>
+    <t>344.00</t>
+  </si>
+  <si>
+    <t>199.00</t>
+  </si>
+  <si>
+    <t>51.00</t>
+  </si>
+  <si>
+    <t>215.00</t>
+  </si>
+  <si>
+    <t>182.00</t>
+  </si>
+  <si>
+    <t>349.00</t>
+  </si>
+  <si>
+    <t>348.00</t>
+  </si>
+  <si>
+    <t>2665-25</t>
+  </si>
+  <si>
+    <t>SF SAUV BLAN 25 6X75 MI SC</t>
+  </si>
+  <si>
+    <t>136.00</t>
+  </si>
+  <si>
+    <t>120.00</t>
+  </si>
+  <si>
+    <t>1,893.00</t>
+  </si>
+  <si>
+    <t>38.00</t>
+  </si>
+  <si>
+    <t>175.00</t>
+  </si>
+  <si>
+    <t>513.00</t>
+  </si>
+  <si>
+    <t>70.00</t>
+  </si>
+  <si>
+    <t>580.00</t>
+  </si>
+  <si>
+    <t>617.00</t>
+  </si>
+  <si>
+    <t>157.00</t>
+  </si>
+  <si>
+    <t>138.00</t>
   </si>
 </sst>
 </file>
@@ -1970,880 +1991,880 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>58</v>
+      <c r="A2">
+        <v>186</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>448</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>60</v>
+      <c r="A3">
+        <v>360</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>63</v>
+      <c r="A4">
+        <v>375</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>66</v>
+      <c r="A5">
+        <v>428</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>442</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>452</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>454</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>456</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>457</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>458</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>459</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>460</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>461</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>526</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>527</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>528</v>
+      </c>
+      <c r="B18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>585</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>586</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>90</v>
-      </c>
-      <c r="B15" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-    </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>105</v>
+      <c r="A21">
+        <v>587</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>431</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>107</v>
+      <c r="A22">
+        <v>1902</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>110</v>
+      <c r="A23">
+        <v>1905</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>113</v>
+      <c r="A24">
+        <v>1915</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>115</v>
+      <c r="A25">
+        <v>1917</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>118</v>
+      <c r="A26">
+        <v>1927</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>121</v>
+      <c r="A27">
+        <v>1928</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>123</v>
+      <c r="A28">
+        <v>1956</v>
       </c>
       <c r="B28" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>125</v>
+      <c r="A29">
+        <v>1957</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>128</v>
+      <c r="A30">
+        <v>1959</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>131</v>
+      <c r="A31">
+        <v>2061</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>134</v>
+      <c r="A32">
+        <v>2271</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>136</v>
+      <c r="A33">
+        <v>2390</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>471</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>148</v>
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>421</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="C39" t="s">
-        <v>472</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="C40" t="s">
-        <v>473</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>455</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>449</v>
+        <v>497</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>434</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>163</v>
+        <v>86</v>
       </c>
       <c r="C45" t="s">
-        <v>164</v>
+        <v>498</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>186</v>
+      <c r="A46" t="s">
+        <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="C46" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>1902</v>
+      <c r="A47" t="s">
+        <v>89</v>
       </c>
       <c r="B47" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C47" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>1905</v>
+      <c r="A48" t="s">
+        <v>92</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>40</v>
+        <v>499</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>1915</v>
+      <c r="A49" t="s">
+        <v>94</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>1917</v>
+      <c r="A50" t="s">
+        <v>96</v>
       </c>
       <c r="B50" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>1927</v>
-      </c>
-      <c r="B51" t="s">
-        <v>44</v>
-      </c>
-      <c r="C51" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>1928</v>
-      </c>
-      <c r="B52" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>1956</v>
-      </c>
-      <c r="B53" t="s">
-        <v>48</v>
-      </c>
-      <c r="C53" t="s">
-        <v>430</v>
-      </c>
-    </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>1957</v>
+      <c r="A54" t="s">
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>1959</v>
+      <c r="A55" t="s">
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C55" t="s">
-        <v>51</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C56" t="s">
-        <v>456</v>
+        <v>424</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>167</v>
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>2061</v>
+      <c r="A58" t="s">
+        <v>116</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>453</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="B59" t="s">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="C59" t="s">
-        <v>434</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>121</v>
       </c>
       <c r="B60" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="C60" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="B61" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="C61" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B63" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>457</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="B65" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B66" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
+        <v>31</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="B68" t="s">
-        <v>191</v>
+        <v>141</v>
       </c>
       <c r="C68" t="s">
-        <v>474</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>143</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>425</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>426</v>
+        <v>149</v>
       </c>
       <c r="C71" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>197</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>198</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="B75" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="C75" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>206</v>
+        <v>158</v>
       </c>
       <c r="B76" t="s">
-        <v>207</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="B77" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>2271</v>
+      <c r="A78" t="s">
+        <v>163</v>
       </c>
       <c r="B78" t="s">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="C78" t="s">
-        <v>55</v>
+        <v>503</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="C79" t="s">
-        <v>212</v>
+        <v>459</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>213</v>
+        <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>504</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="B81" t="s">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="C81" t="s">
         <v>427</v>
@@ -2851,54 +2872,54 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>218</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>444</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>441</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
-        <v>442</v>
+        <v>181</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
@@ -2906,736 +2927,736 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="C87" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="C89" t="s">
-        <v>230</v>
+        <v>505</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
       <c r="B90" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>235</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>236</v>
+        <v>192</v>
       </c>
       <c r="B91" t="s">
-        <v>237</v>
+        <v>193</v>
       </c>
       <c r="C91" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>238</v>
+        <v>417</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>418</v>
       </c>
       <c r="C92" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>195</v>
       </c>
       <c r="C93" t="s">
-        <v>458</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>243</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="C94" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="B95" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="C95" t="s">
-        <v>459</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="B96" t="s">
-        <v>248</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="C97" t="s">
-        <v>475</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="C98" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>255</v>
+        <v>211</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>212</v>
       </c>
       <c r="C100" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>164</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>460</v>
+        <v>215</v>
       </c>
       <c r="B102" t="s">
-        <v>461</v>
+        <v>216</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>462</v>
+        <v>217</v>
       </c>
       <c r="B103" t="s">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>2390</v>
+      <c r="A104" t="s">
+        <v>219</v>
       </c>
       <c r="B104" t="s">
-        <v>56</v>
+        <v>220</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="B105" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>261</v>
+        <v>432</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>433</v>
       </c>
       <c r="C106" t="s">
-        <v>477</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>224</v>
       </c>
       <c r="C107" t="s">
-        <v>450</v>
+        <v>225</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="C108" t="s">
-        <v>438</v>
+        <v>228</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>464</v>
+        <v>229</v>
       </c>
       <c r="B109" t="s">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="C109" t="s">
-        <v>478</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>268</v>
+        <v>231</v>
       </c>
       <c r="B110" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
       <c r="C110" t="s">
-        <v>479</v>
+        <v>233</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="C111" t="s">
-        <v>443</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>272</v>
+        <v>506</v>
       </c>
       <c r="B112" t="s">
-        <v>273</v>
+        <v>507</v>
       </c>
       <c r="C112" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="B113" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="C113" t="s">
-        <v>230</v>
+        <v>425</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="B114" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="C114" t="s">
-        <v>278</v>
+        <v>508</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="B115" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="C115" t="s">
-        <v>394</v>
+        <v>42</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="B116" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="C116" t="s">
-        <v>203</v>
+        <v>420</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="B117" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="C117" t="s">
-        <v>242</v>
+        <v>201</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>285</v>
+        <v>247</v>
       </c>
       <c r="B118" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="C118" t="s">
-        <v>443</v>
+        <v>509</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>249</v>
       </c>
       <c r="B119" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
       <c r="C119" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="B120" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="C120" t="s">
-        <v>439</v>
+        <v>201</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="B121" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="C121" t="s">
-        <v>294</v>
+        <v>510</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="B122" t="s">
-        <v>296</v>
+        <v>256</v>
       </c>
       <c r="C122" t="s">
-        <v>452</v>
+        <v>162</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>299</v>
+        <v>445</v>
       </c>
       <c r="B123" t="s">
-        <v>300</v>
+        <v>446</v>
       </c>
       <c r="C123" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="B124" t="s">
-        <v>302</v>
+        <v>448</v>
       </c>
       <c r="C124" t="s">
-        <v>75</v>
+        <v>511</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>297</v>
+        <v>257</v>
       </c>
       <c r="B125" t="s">
-        <v>298</v>
+        <v>258</v>
       </c>
       <c r="C125" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="B126" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="C126" t="s">
-        <v>75</v>
+        <v>512</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="B127" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="C127" t="s">
-        <v>480</v>
+        <v>513</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="B128" t="s">
-        <v>308</v>
+        <v>264</v>
       </c>
       <c r="C128" t="s">
-        <v>267</v>
+        <v>430</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>309</v>
+        <v>449</v>
       </c>
       <c r="B129" t="s">
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="C129" t="s">
-        <v>436</v>
+        <v>514</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="B130" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="C130" t="s">
-        <v>11</v>
+        <v>457</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>313</v>
+        <v>268</v>
       </c>
       <c r="B131" t="s">
-        <v>314</v>
+        <v>269</v>
       </c>
       <c r="C131" t="s">
-        <v>315</v>
+        <v>434</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="B132" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="B133" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="C133" t="s">
-        <v>320</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>321</v>
+        <v>274</v>
       </c>
       <c r="B134" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>324</v>
+        <v>516</v>
       </c>
       <c r="B135" t="s">
-        <v>325</v>
+        <v>517</v>
       </c>
       <c r="C135" t="s">
-        <v>481</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>331</v>
+        <v>276</v>
       </c>
       <c r="B136" t="s">
-        <v>332</v>
+        <v>277</v>
       </c>
       <c r="C136" t="s">
-        <v>330</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>326</v>
+        <v>278</v>
       </c>
       <c r="B137" t="s">
-        <v>327</v>
+        <v>279</v>
       </c>
       <c r="C137" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>280</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="C138" t="s">
-        <v>130</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="B139" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="C139" t="s">
-        <v>75</v>
+        <v>434</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="B140" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>286</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="B141" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="C141" t="s">
-        <v>65</v>
+        <v>431</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="B142" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
+        <v>291</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="B143" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>23</v>
+        <v>442</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="B144" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="C144" t="s">
-        <v>482</v>
+        <v>26</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="B145" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="C145" t="s">
-        <v>203</v>
+        <v>107</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="B146" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="C146" t="s">
-        <v>320</v>
+        <v>75</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="B147" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="C147" t="s">
-        <v>203</v>
+        <v>75</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>444</v>
+        <v>302</v>
       </c>
       <c r="B148" t="s">
-        <v>445</v>
+        <v>303</v>
       </c>
       <c r="C148" t="s">
-        <v>401</v>
+        <v>518</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>360</v>
+      <c r="A149" t="s">
+        <v>304</v>
       </c>
       <c r="B149" t="s">
-        <v>5</v>
+        <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>452</v>
+        <v>265</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>375</v>
+      <c r="A150" t="s">
+        <v>306</v>
       </c>
       <c r="B150" t="s">
-        <v>7</v>
+        <v>307</v>
       </c>
       <c r="C150" t="s">
-        <v>323</v>
+        <v>519</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="B151" t="s">
-        <v>352</v>
+        <v>309</v>
       </c>
       <c r="C151" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="B152" t="s">
-        <v>354</v>
+        <v>311</v>
       </c>
       <c r="C152" t="s">
-        <v>355</v>
+        <v>312</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>446</v>
+        <v>313</v>
       </c>
       <c r="B153" t="s">
-        <v>447</v>
+        <v>314</v>
       </c>
       <c r="C153" t="s">
         <v>13</v>
@@ -3643,505 +3664,505 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="B154" t="s">
-        <v>357</v>
+        <v>316</v>
       </c>
       <c r="C154" t="s">
-        <v>358</v>
+        <v>317</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>466</v>
+        <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>467</v>
+        <v>319</v>
       </c>
       <c r="C155" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="B156" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="C156" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>361</v>
+        <v>323</v>
       </c>
       <c r="B157" t="s">
-        <v>362</v>
+        <v>324</v>
       </c>
       <c r="C157" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="B158" t="s">
-        <v>364</v>
+        <v>326</v>
       </c>
       <c r="C158" t="s">
-        <v>468</v>
+        <v>128</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159">
-        <v>428</v>
+      <c r="A159" t="s">
+        <v>328</v>
       </c>
       <c r="B159" t="s">
-        <v>8</v>
+        <v>329</v>
       </c>
       <c r="C159" t="s">
-        <v>227</v>
+        <v>327</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="B160" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="C160" t="s">
-        <v>437</v>
+        <v>75</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161">
-        <v>442</v>
+      <c r="A161" t="s">
+        <v>332</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="C161" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162">
-        <v>452</v>
+      <c r="A162" t="s">
+        <v>334</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>335</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163">
-        <v>453</v>
+      <c r="A163" t="s">
+        <v>336</v>
       </c>
       <c r="B163" t="s">
-        <v>14</v>
+        <v>337</v>
       </c>
       <c r="C163" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164">
-        <v>454</v>
+      <c r="A164" t="s">
+        <v>338</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>339</v>
       </c>
       <c r="C164" t="s">
-        <v>17</v>
+        <v>520</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165">
-        <v>456</v>
+      <c r="A165" t="s">
+        <v>340</v>
       </c>
       <c r="B165" t="s">
-        <v>18</v>
+        <v>341</v>
       </c>
       <c r="C165" t="s">
-        <v>19</v>
+        <v>201</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166">
-        <v>457</v>
+      <c r="A166" t="s">
+        <v>342</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>26</v>
+        <v>521</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167">
-        <v>458</v>
+      <c r="A167" t="s">
+        <v>435</v>
       </c>
       <c r="B167" t="s">
-        <v>22</v>
+        <v>436</v>
       </c>
       <c r="C167" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>344</v>
+      </c>
+      <c r="B168" t="s">
+        <v>345</v>
+      </c>
+      <c r="C168" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168">
-        <v>459</v>
-      </c>
-      <c r="B168" t="s">
-        <v>24</v>
-      </c>
-      <c r="C168" t="s">
-        <v>355</v>
-      </c>
-    </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169">
-        <v>460</v>
+      <c r="A169" t="s">
+        <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>25</v>
+        <v>347</v>
       </c>
       <c r="C169" t="s">
-        <v>203</v>
+        <v>348</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170">
-        <v>461</v>
+      <c r="A170" t="s">
+        <v>349</v>
       </c>
       <c r="B170" t="s">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>351</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>367</v>
+        <v>437</v>
       </c>
       <c r="B171" t="s">
-        <v>368</v>
+        <v>438</v>
       </c>
       <c r="C171" t="s">
-        <v>484</v>
+        <v>523</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="C172" t="s">
-        <v>31</v>
+        <v>524</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>371</v>
+        <v>451</v>
       </c>
       <c r="B173" t="s">
-        <v>372</v>
+        <v>452</v>
       </c>
       <c r="C173" t="s">
-        <v>485</v>
+        <v>351</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="B174" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C174" t="s">
-        <v>38</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="B175" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="C175" t="s">
-        <v>486</v>
+        <v>525</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="B176" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="C176" t="s">
-        <v>203</v>
+        <v>429</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="B177" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="C177" t="s">
-        <v>381</v>
+        <v>526</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="B178" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="C178" t="s">
-        <v>384</v>
+        <v>31</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B179" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="C179" t="s">
-        <v>358</v>
+        <v>460</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B180" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="C180" t="s">
-        <v>451</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B181" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="C181" t="s">
-        <v>391</v>
+        <v>461</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>469</v>
+        <v>370</v>
       </c>
       <c r="B182" t="s">
-        <v>470</v>
+        <v>371</v>
       </c>
       <c r="C182" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B183" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="C183" t="s">
-        <v>394</v>
+        <v>527</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="B184" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="C184" t="s">
-        <v>65</v>
+        <v>377</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="C185" t="s">
-        <v>428</v>
+        <v>351</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="B186" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
-        <v>487</v>
+        <v>441</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="C187" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>399</v>
+        <v>453</v>
       </c>
       <c r="B188" t="s">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="C188" t="s">
-        <v>401</v>
+        <v>456</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="B189" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C189" t="s">
-        <v>26</v>
+        <v>387</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="C190" t="s">
-        <v>381</v>
+        <v>65</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C191" t="s">
-        <v>35</v>
+        <v>420</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="C192" t="s">
-        <v>435</v>
+        <v>394</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193">
-        <v>526</v>
+      <c r="A193" t="s">
+        <v>395</v>
       </c>
       <c r="B193" t="s">
-        <v>29</v>
+        <v>396</v>
       </c>
       <c r="C193" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194">
-        <v>527</v>
+      <c r="A194" t="s">
+        <v>397</v>
       </c>
       <c r="B194" t="s">
-        <v>30</v>
+        <v>398</v>
       </c>
       <c r="C194" t="s">
-        <v>422</v>
+        <v>374</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195">
+      <c r="A195" t="s">
+        <v>399</v>
+      </c>
+      <c r="B195" t="s">
+        <v>400</v>
+      </c>
+      <c r="C195" t="s">
         <v>528</v>
       </c>
-      <c r="B195" t="s">
-        <v>32</v>
-      </c>
-      <c r="C195" t="s">
-        <v>438</v>
-      </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196">
-        <v>585</v>
+      <c r="A196" t="s">
+        <v>401</v>
       </c>
       <c r="B196" t="s">
-        <v>33</v>
+        <v>402</v>
       </c>
       <c r="C196" t="s">
-        <v>23</v>
+        <v>425</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197">
-        <v>586</v>
+      <c r="A197" t="s">
+        <v>403</v>
       </c>
       <c r="B197" t="s">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="C197" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198">
-        <v>587</v>
+      <c r="A198" t="s">
+        <v>405</v>
       </c>
       <c r="B198" t="s">
-        <v>36</v>
+        <v>406</v>
       </c>
       <c r="C198" t="s">
-        <v>26</v>
+        <v>427</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="B199" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C199" t="s">
         <v>11</v>
@@ -4149,21 +4170,21 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="B200" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="C200" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="B201" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="C201" t="s">
         <v>11</v>
@@ -4171,76 +4192,76 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B202" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="C202" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="B203" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="C203" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="B204" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="C204" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="B205" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="C205" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="B206" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="C206" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="B207" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C207" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="B208" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="C208" t="s">
         <v>75</v>
@@ -4248,10 +4269,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="B209" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="C209" t="s">
         <v>21</v>
@@ -4259,65 +4280,65 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="B210" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="C210" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="B211" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="C211" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="B212" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="C212" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="B213" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="C213" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="B214" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="C214" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="B215" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="C215" t="s">
         <v>13</v>
@@ -4325,10 +4346,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="B216" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="C216" t="s">
         <v>13</v>
@@ -4336,10 +4357,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="B217" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="C217" t="s">
         <v>23</v>
